--- a/resources/pet/pet_spell_book.xlsx
+++ b/resources/pet/pet_spell_book.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\重要文档\RoundCA\data_table\normal\pet\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PetSpellBook" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
+    <sheet name="PetSpellBook" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">PetSpellBook!#REF!</definedName>
@@ -233,79 +239,151 @@
     <definedName name="Z_FAF1ADB8_46A9_40B0_AA1B_9C75E39038F2_.wvu.FilterData" localSheetId="1" hidden="1">PetSpellBook!$A$1:$C$7</definedName>
     <definedName name="Z_FF6A625A_6008_4A1D_8FF0_F8A30B9F02A0_.wvu.FilterData" localSheetId="1" hidden="1">PetSpellBook!$A$1:$C$7</definedName>
   </definedNames>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+  <si>
+    <t>表名</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>列作用说明</t>
+  </si>
+  <si>
+    <t>生成文件</t>
+  </si>
+  <si>
+    <t>填表说明</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>_desc:string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出目标</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要导出的sheet</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出文件</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SERVER</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLIENT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵兽兽决配置表</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽决道具id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>PetSpellBook</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>pet/pet_spell_book.py</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得能力id</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ability_id:int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,13 +395,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999816888943144"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999938962981048"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -353,102 +431,102 @@
     </border>
   </borders>
   <cellStyleXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1"/>
+    <cellStyle name="常规 11" xfId="11"/>
+    <cellStyle name="常规 2" xfId="4"/>
     <cellStyle name="常规 2 2" xfId="2"/>
     <cellStyle name="常规 2 3" xfId="3"/>
-    <cellStyle name="常规 2" xfId="4"/>
     <cellStyle name="常规 3" xfId="5"/>
     <cellStyle name="常规 4" xfId="6"/>
     <cellStyle name="常规 5" xfId="7"/>
+    <cellStyle name="常规 6" xfId="1"/>
+    <cellStyle name="常规 7" xfId="10"/>
     <cellStyle name="常规_CONFIG" xfId="8"/>
     <cellStyle name="常规_Sheet1" xfId="9"/>
-    <cellStyle name="常规 7" xfId="10"/>
-    <cellStyle name="常规 11" xfId="11"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -473,74 +551,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -801,1225 +819,1175 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="21.125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="49.5" customWidth="1" style="8" min="3" max="3"/>
-    <col width="30.125" customWidth="1" style="8" min="4" max="4"/>
-    <col width="23.5" customWidth="1" style="8" min="5" max="5"/>
-    <col width="19.25" customWidth="1" style="8" min="6" max="6"/>
-    <col width="21.375" customWidth="1" style="8" min="8" max="8"/>
+    <col min="1" max="1" width="21.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="30.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.25" style="8" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="8">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>表名</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>灵兽兽决配置表</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="8">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" s="8">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>列作用说明</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>导出目标</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>需要导出的sheet</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>导出文件</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="n"/>
-      <c r="H3" s="0" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>生成文件</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>PetSpellBook</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>pet/pet_spell_book.py</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CLIENT</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>PetSpellBook</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>pet/pet_spell_book.py</t>
-        </is>
+    <row r="1" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3" s="8"/>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D133"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C133"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
-    <col width="18.75" customWidth="1" style="9" min="2" max="3"/>
-    <col width="9" customWidth="1" style="13" min="4" max="16384"/>
+    <col min="1" max="1" width="16.75" style="9" customWidth="1"/>
+    <col min="2" max="3" width="18.75" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="64.5" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>兽决道具id</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>填表说明</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>获得能力id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36.75" customFormat="1" customHeight="1" s="15">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>item_id:int</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>_desc:string</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>ability_id:int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-    </row>
-    <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="A5" s="16" t="n">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="15" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+    </row>
+    <row r="4" spans="1:3" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="16">
         <v>21000</v>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="17" t="n">
+      <c r="B5" s="11"/>
+      <c r="C5" s="17">
         <v>5001</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="8">
-      <c r="A6" s="16" t="n">
+    <row r="6" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16">
         <v>21001</v>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="17" t="n">
+      <c r="B6" s="11"/>
+      <c r="C6" s="17">
         <v>5002</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="8">
-      <c r="A7" s="16" t="n">
+    <row r="7" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16">
         <v>21002</v>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="17" t="n">
+      <c r="B7" s="11"/>
+      <c r="C7" s="17">
         <v>5003</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A8" s="16">
         <v>21003</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="17">
         <v>5004</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A9" s="16">
         <v>21004</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="17">
         <v>5005</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A10" s="16">
         <v>21005</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="17">
         <v>5006</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A11" s="16">
         <v>21006</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="17">
         <v>5007</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A12" s="16">
         <v>21007</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="17">
         <v>5008</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A13" s="16">
         <v>21008</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="17">
         <v>5009</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A14" s="16">
         <v>21009</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="17">
         <v>5010</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A15" s="16">
         <v>21010</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="17">
         <v>5011</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A16" s="16">
         <v>21011</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="17">
         <v>5012</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A17" s="16">
         <v>21012</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="17">
         <v>5013</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="n">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A18" s="16">
         <v>21013</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="17">
         <v>5014</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="n">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A19" s="16">
         <v>21014</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="17">
         <v>5015</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="n">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A20" s="16">
         <v>21015</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="17">
         <v>5016</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="n">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A21" s="16">
         <v>21016</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="17">
         <v>5017</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="n">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A22" s="16">
         <v>21017</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="17">
         <v>5018</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="16" t="n">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A23" s="16">
         <v>21018</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="17">
         <v>5019</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="16" t="n">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A24" s="16">
         <v>21019</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="17">
         <v>5020</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="n">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A25" s="16">
         <v>21020</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="17">
         <v>5021</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="n">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A26" s="16">
         <v>21021</v>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="17">
         <v>5022</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="16" t="n">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A27" s="16">
         <v>21022</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="17">
         <v>5023</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="16" t="n">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A28" s="16">
         <v>21023</v>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="17">
         <v>5024</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="16" t="n">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A29" s="16">
         <v>21024</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="17">
         <v>5025</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="n">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A30" s="16">
         <v>21025</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="17">
         <v>5026</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="16" t="n">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A31" s="16">
         <v>21026</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="17">
         <v>5027</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="16" t="n">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A32" s="16">
         <v>21027</v>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C32" s="17">
         <v>5028</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="16" t="n">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="16">
         <v>21028</v>
       </c>
-      <c r="C33" s="17" t="n">
+      <c r="C33" s="17">
         <v>5029</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="16" t="n">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="16">
         <v>21029</v>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C34" s="17">
         <v>5030</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="n">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" s="16">
         <v>21030</v>
       </c>
-      <c r="C35" s="17" t="n">
+      <c r="C35" s="17">
         <v>5031</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="n">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A36" s="16">
         <v>21031</v>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C36" s="17">
         <v>5032</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="n">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="16">
         <v>21032</v>
       </c>
-      <c r="C37" s="17" t="n">
+      <c r="C37" s="17">
         <v>5033</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="16" t="n">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" s="16">
         <v>21033</v>
       </c>
-      <c r="C38" s="17" t="n">
+      <c r="C38" s="17">
         <v>5034</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="16" t="n">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A39" s="16">
         <v>21034</v>
       </c>
-      <c r="C39" s="17" t="n">
+      <c r="C39" s="17">
         <v>5035</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="16" t="n">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A40" s="16">
         <v>21035</v>
       </c>
-      <c r="C40" s="17" t="n">
+      <c r="C40" s="17">
         <v>5036</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="n">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A41" s="16">
         <v>21036</v>
       </c>
-      <c r="C41" s="17" t="n">
+      <c r="C41" s="17">
         <v>5037</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="16" t="n">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A42" s="16">
         <v>21037</v>
       </c>
-      <c r="C42" s="17" t="n">
+      <c r="C42" s="17">
         <v>5038</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="16" t="n">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" s="16">
         <v>21038</v>
       </c>
-      <c r="C43" s="17" t="n">
+      <c r="C43" s="17">
         <v>5039</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="16" t="n">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" s="16">
         <v>21039</v>
       </c>
-      <c r="C44" s="17" t="n">
+      <c r="C44" s="17">
         <v>5040</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="16" t="n">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" s="16">
         <v>21040</v>
       </c>
-      <c r="C45" s="17" t="n">
+      <c r="C45" s="17">
         <v>5041</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="n">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="16">
         <v>21041</v>
       </c>
-      <c r="C46" s="17" t="n">
+      <c r="C46" s="17">
         <v>5042</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="16" t="n">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" s="16">
         <v>21042</v>
       </c>
-      <c r="C47" s="17" t="n">
+      <c r="C47" s="17">
         <v>5043</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="16" t="n">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="16">
         <v>21043</v>
       </c>
-      <c r="C48" s="17" t="n">
+      <c r="C48" s="17">
         <v>5044</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="16" t="n">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A49" s="16">
         <v>21044</v>
       </c>
-      <c r="C49" s="17" t="n">
+      <c r="C49" s="17">
         <v>5045</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="16" t="n">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" s="16">
         <v>21045</v>
       </c>
-      <c r="C50" s="17" t="n">
+      <c r="C50" s="17">
         <v>5046</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="16" t="n">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A51" s="16">
         <v>21046</v>
       </c>
-      <c r="C51" s="17" t="n">
+      <c r="C51" s="17">
         <v>5047</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="16" t="n">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A52" s="16">
         <v>21047</v>
       </c>
-      <c r="C52" s="17" t="n">
+      <c r="C52" s="17">
         <v>5048</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="n">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A53" s="16">
         <v>21048</v>
       </c>
-      <c r="C53" s="17" t="n">
+      <c r="C53" s="17">
         <v>5049</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="16" t="n">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A54" s="16">
         <v>21049</v>
       </c>
-      <c r="C54" s="17" t="n">
+      <c r="C54" s="17">
         <v>5050</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="16" t="n">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A55" s="16">
         <v>21050</v>
       </c>
-      <c r="C55" s="17" t="n">
+      <c r="C55" s="17">
         <v>5051</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="16" t="n">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A56" s="16">
         <v>21051</v>
       </c>
-      <c r="C56" s="17" t="n">
+      <c r="C56" s="17">
         <v>5052</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="16" t="n">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A57" s="16">
         <v>21052</v>
       </c>
-      <c r="C57" s="17" t="n">
+      <c r="C57" s="17">
         <v>5053</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="16" t="n">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A58" s="16">
         <v>21053</v>
       </c>
-      <c r="C58" s="17" t="n">
+      <c r="C58" s="17">
         <v>5054</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="16" t="n">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A59" s="16">
         <v>21054</v>
       </c>
-      <c r="C59" s="17" t="n">
+      <c r="C59" s="17">
         <v>5055</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="16" t="n">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A60" s="16">
         <v>21055</v>
       </c>
-      <c r="C60" s="17" t="n">
+      <c r="C60" s="17">
         <v>5056</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="16" t="n">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A61" s="16">
         <v>21056</v>
       </c>
-      <c r="C61" s="17" t="n">
+      <c r="C61" s="17">
         <v>5057</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="16" t="n">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A62" s="16">
         <v>21057</v>
       </c>
-      <c r="C62" s="17" t="n">
+      <c r="C62" s="17">
         <v>5501</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="16" t="n">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A63" s="16">
         <v>21058</v>
       </c>
-      <c r="C63" s="17" t="n">
+      <c r="C63" s="17">
         <v>5502</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="16" t="n">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A64" s="16">
         <v>21059</v>
       </c>
-      <c r="C64" s="17" t="n">
+      <c r="C64" s="17">
         <v>5503</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="16" t="n">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A65" s="16">
         <v>21060</v>
       </c>
-      <c r="C65" s="17" t="n">
+      <c r="C65" s="17">
         <v>5504</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="16" t="n">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A66" s="16">
         <v>21061</v>
       </c>
-      <c r="C66" s="17" t="n">
+      <c r="C66" s="17">
         <v>5505</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="16" t="n">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A67" s="16">
         <v>21062</v>
       </c>
-      <c r="C67" s="17" t="n">
+      <c r="C67" s="17">
         <v>6551</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="16" t="n">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A68" s="16">
         <v>21063</v>
       </c>
-      <c r="C68" s="17" t="n">
+      <c r="C68" s="17">
         <v>6552</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="16" t="n">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A69" s="16">
         <v>21064</v>
       </c>
-      <c r="C69" s="17" t="n">
+      <c r="C69" s="17">
         <v>6553</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="16" t="n">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A70" s="16">
         <v>21065</v>
       </c>
-      <c r="C70" s="17" t="n">
+      <c r="C70" s="17">
         <v>6554</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="16" t="n">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A71" s="16">
         <v>21066</v>
       </c>
-      <c r="C71" s="17" t="n">
+      <c r="C71" s="17">
         <v>6555</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="16" t="n">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A72" s="16">
         <v>21067</v>
       </c>
-      <c r="C72" s="17" t="n">
+      <c r="C72" s="17">
         <v>6556</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="16" t="n">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A73" s="16">
         <v>21068</v>
       </c>
-      <c r="C73" s="17" t="n">
+      <c r="C73" s="17">
         <v>6557</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="16" t="n">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A74" s="16">
         <v>21069</v>
       </c>
-      <c r="C74" s="17" t="n">
+      <c r="C74" s="17">
         <v>6558</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="16" t="n">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A75" s="16">
         <v>21070</v>
       </c>
-      <c r="C75" s="17" t="n">
+      <c r="C75" s="17">
         <v>6559</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="16" t="n">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A76" s="16">
         <v>21071</v>
       </c>
-      <c r="C76" s="17" t="n">
+      <c r="C76" s="17">
         <v>6560</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="16" t="n">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A77" s="16">
         <v>21072</v>
       </c>
-      <c r="C77" s="17" t="n">
+      <c r="C77" s="17">
         <v>6001</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="16" t="n">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A78" s="16">
         <v>21073</v>
       </c>
-      <c r="C78" s="17" t="n">
+      <c r="C78" s="17">
         <v>6002</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="16" t="n">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A79" s="16">
         <v>21074</v>
       </c>
-      <c r="C79" s="17" t="n">
+      <c r="C79" s="17">
         <v>6003</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="16" t="n">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A80" s="16">
         <v>21075</v>
       </c>
-      <c r="C80" s="17" t="n">
+      <c r="C80" s="17">
         <v>6004</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="16" t="n">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A81" s="16">
         <v>21076</v>
       </c>
-      <c r="C81" s="17" t="n">
+      <c r="C81" s="17">
         <v>6005</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="16" t="n">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A82" s="16">
         <v>21077</v>
       </c>
-      <c r="C82" s="17" t="n">
+      <c r="C82" s="17">
         <v>6006</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="16" t="n">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A83" s="16">
         <v>21078</v>
       </c>
-      <c r="C83" s="17" t="n">
+      <c r="C83" s="17">
         <v>6007</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="16" t="n">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A84" s="16">
         <v>21079</v>
       </c>
-      <c r="C84" s="17" t="n">
+      <c r="C84" s="17">
         <v>6008</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="16" t="n">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A85" s="16">
         <v>21080</v>
       </c>
-      <c r="C85" s="17" t="n">
+      <c r="C85" s="17">
         <v>6009</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="16" t="n">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A86" s="16">
         <v>21081</v>
       </c>
-      <c r="C86" s="17" t="n">
+      <c r="C86" s="17">
         <v>6010</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="16" t="n">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A87" s="16">
         <v>21082</v>
       </c>
-      <c r="C87" s="17" t="n">
+      <c r="C87" s="17">
         <v>6011</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="16" t="n">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A88" s="16">
         <v>21083</v>
       </c>
-      <c r="C88" s="17" t="n">
+      <c r="C88" s="17">
         <v>6012</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="16" t="n">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A89" s="16">
         <v>21084</v>
       </c>
-      <c r="C89" s="17" t="n">
+      <c r="C89" s="17">
         <v>6013</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="16" t="n">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A90" s="16">
         <v>21085</v>
       </c>
-      <c r="C90" s="17" t="n">
+      <c r="C90" s="17">
         <v>6014</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="16" t="n">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A91" s="16">
         <v>21086</v>
       </c>
-      <c r="C91" s="17" t="n">
+      <c r="C91" s="17">
         <v>6015</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="16" t="n">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A92" s="16">
         <v>21087</v>
       </c>
-      <c r="C92" s="17" t="n">
+      <c r="C92" s="17">
         <v>6016</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="16" t="n">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A93" s="16">
         <v>21088</v>
       </c>
-      <c r="C93" s="17" t="n">
+      <c r="C93" s="17">
         <v>6017</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="16" t="n">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A94" s="16">
         <v>21089</v>
       </c>
-      <c r="C94" s="17" t="n">
+      <c r="C94" s="17">
         <v>6018</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="16" t="n">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A95" s="16">
         <v>21090</v>
       </c>
-      <c r="C95" s="17" t="n">
+      <c r="C95" s="17">
         <v>6019</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="16" t="n">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A96" s="16">
         <v>21091</v>
       </c>
-      <c r="C96" s="17" t="n">
+      <c r="C96" s="17">
         <v>6020</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="16" t="n">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A97" s="16">
         <v>21092</v>
       </c>
-      <c r="C97" s="17" t="n">
+      <c r="C97" s="17">
         <v>6021</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="16" t="n">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A98" s="16">
         <v>21093</v>
       </c>
-      <c r="C98" s="17" t="n">
+      <c r="C98" s="17">
         <v>6022</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="16" t="n">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A99" s="16">
         <v>21094</v>
       </c>
-      <c r="C99" s="17" t="n">
+      <c r="C99" s="17">
         <v>6023</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="16" t="n">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A100" s="16">
         <v>21095</v>
       </c>
-      <c r="C100" s="17" t="n">
+      <c r="C100" s="17">
         <v>6024</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="16" t="n">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A101" s="16">
         <v>21096</v>
       </c>
-      <c r="C101" s="17" t="n">
+      <c r="C101" s="17">
         <v>6025</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="16" t="n">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A102" s="16">
         <v>21097</v>
       </c>
-      <c r="C102" s="17" t="n">
+      <c r="C102" s="17">
         <v>6026</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="16" t="n">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A103" s="16">
         <v>21098</v>
       </c>
-      <c r="C103" s="17" t="n">
+      <c r="C103" s="17">
         <v>6027</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="16" t="n">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A104" s="16">
         <v>21099</v>
       </c>
-      <c r="C104" s="17" t="n">
+      <c r="C104" s="17">
         <v>6028</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="16" t="n">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A105" s="16">
         <v>21100</v>
       </c>
-      <c r="C105" s="17" t="n">
+      <c r="C105" s="17">
         <v>6029</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="16" t="n">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A106" s="16">
         <v>21101</v>
       </c>
-      <c r="C106" s="17" t="n">
+      <c r="C106" s="17">
         <v>6030</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="16" t="n">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A107" s="16">
         <v>21102</v>
       </c>
-      <c r="C107" s="17" t="n">
+      <c r="C107" s="17">
         <v>6031</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="16" t="n">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A108" s="16">
         <v>21103</v>
       </c>
-      <c r="C108" s="17" t="n">
+      <c r="C108" s="17">
         <v>6032</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="16" t="n">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A109" s="16">
         <v>21104</v>
       </c>
-      <c r="C109" s="17" t="n">
+      <c r="C109" s="17">
         <v>6033</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="16" t="n">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A110" s="16">
         <v>21105</v>
       </c>
-      <c r="C110" s="17" t="n">
+      <c r="C110" s="17">
         <v>6034</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="16" t="n">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A111" s="16">
         <v>21106</v>
       </c>
-      <c r="C111" s="17" t="n">
+      <c r="C111" s="17">
         <v>6035</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="16" t="n">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A112" s="16">
         <v>21107</v>
       </c>
-      <c r="C112" s="17" t="n">
+      <c r="C112" s="17">
         <v>6036</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="16" t="n">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A113" s="16">
         <v>21108</v>
       </c>
-      <c r="C113" s="17" t="n">
+      <c r="C113" s="17">
         <v>6037</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="16" t="n">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A114" s="16">
         <v>21109</v>
       </c>
-      <c r="C114" s="17" t="n">
+      <c r="C114" s="17">
         <v>6038</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="16" t="n">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A115" s="16">
         <v>21110</v>
       </c>
-      <c r="C115" s="17" t="n">
+      <c r="C115" s="17">
         <v>6039</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="16" t="n">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A116" s="16">
         <v>21111</v>
       </c>
-      <c r="C116" s="17" t="n">
+      <c r="C116" s="17">
         <v>6040</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="16" t="n">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A117" s="16">
         <v>21112</v>
       </c>
-      <c r="C117" s="17" t="n">
+      <c r="C117" s="17">
         <v>6041</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="n">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A118" s="16">
         <v>21113</v>
       </c>
-      <c r="C118" s="17" t="n">
+      <c r="C118" s="17">
         <v>6042</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="16" t="n">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A119" s="16">
         <v>21114</v>
       </c>
-      <c r="C119" s="17" t="n">
+      <c r="C119" s="17">
         <v>6043</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="16" t="n">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A120" s="16">
         <v>21115</v>
       </c>
-      <c r="C120" s="17" t="n">
+      <c r="C120" s="17">
         <v>6044</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="16" t="n">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A121" s="16">
         <v>21116</v>
       </c>
-      <c r="C121" s="17" t="n">
+      <c r="C121" s="17">
         <v>6045</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="16" t="n">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A122" s="16">
         <v>21117</v>
       </c>
-      <c r="C122" s="17" t="n">
+      <c r="C122" s="17">
         <v>6046</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="16" t="n">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A123" s="16">
         <v>21118</v>
       </c>
-      <c r="C123" s="17" t="n">
+      <c r="C123" s="17">
         <v>6047</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="16" t="n">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A124" s="16">
         <v>21119</v>
       </c>
-      <c r="C124" s="17" t="n">
+      <c r="C124" s="17">
         <v>6048</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="16" t="n">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A125" s="16">
         <v>21120</v>
       </c>
-      <c r="C125" s="17" t="n">
+      <c r="C125" s="17">
         <v>6049</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="16" t="n">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A126" s="16">
         <v>21121</v>
       </c>
-      <c r="C126" s="17" t="n">
+      <c r="C126" s="17">
         <v>6050</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="16" t="n">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A127" s="16">
         <v>21122</v>
       </c>
-      <c r="C127" s="17" t="n">
+      <c r="C127" s="17">
         <v>6051</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="16" t="n">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A128" s="16">
         <v>21123</v>
       </c>
-      <c r="C128" s="17" t="n">
+      <c r="C128" s="17">
         <v>6052</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="16" t="n">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A129" s="16">
         <v>21124</v>
       </c>
-      <c r="C129" s="17" t="n">
+      <c r="C129" s="17">
         <v>6053</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="16" t="n">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A130" s="16">
         <v>21125</v>
       </c>
-      <c r="C130" s="17" t="n">
+      <c r="C130" s="17">
         <v>6054</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="16" t="n">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A131" s="16">
         <v>21126</v>
       </c>
-      <c r="C131" s="17" t="n">
+      <c r="C131" s="17">
         <v>6055</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="16" t="n">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A132" s="16">
         <v>21127</v>
       </c>
-      <c r="C132" s="17" t="n">
+      <c r="C132" s="17">
         <v>6056</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="16" t="n">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A133" s="16">
         <v>21128</v>
       </c>
-      <c r="C133" s="17" t="n">
+      <c r="C133" s="17">
         <v>6057</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A4 A134:A1048576">
-    <cfRule type="duplicateValues" priority="1969" dxfId="0"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="A134:A1048576 A1:A4">
+    <cfRule type="duplicateValues" dxfId="1" priority="1969"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C4">
-    <cfRule type="duplicateValues" priority="1975" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1975"/>
   </conditionalFormatting>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>